--- a/astro-site/public/dl/pastry-shop-checklist-templates/08-pastry-shop-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/08-pastry-shop-opening-closing-checklist.xlsx
@@ -916,13 +916,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="62.1" customHeight="1">
+    <row r="5" ht="77.25" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Disarm the alarm and turn on the refrigerated bakery cases: log the reading (41 °F or below, FDA Food Code 3-501.16) at least 45 minutes before stocking (→ 13 Temperature &amp; Receiving Logs · sheet "Temperature Log")</t>
+          <t>Disarm the shop alarm zone (if the kitchen hasn't already) and turn on the refrigerated bakery cases: log the reading (41 °F or below, FDA Food Code 3-501.16) at least 45 minutes before stocking (→ 13 Temperature &amp; Receiving Logs · sheet "Temperature Log")</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -1196,13 +1196,13 @@
       <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="63" customHeight="1">
       <c r="A15" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Stock the case in order: viennoiserie first, then refrigerated pastries, savory last</t>
+          <t>Stock the cases in order: viennoiserie first, then the refrigerated case (cream-filled pastries), savory last: quiche, empanadas and ham &amp; cheese croissants also go in the refrigerated case at 41 °F or below (FDA Food Code 3-501.16)</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Raise the security gate (shutters) and open the door to the public</t>
+          <t>Raise the roll-down security gate (if you have one) and open the door to the public</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Lower the security gate (shutters), turn off the lights and set the alarm</t>
+          <t>Lower the roll-down security gate (if you have one), turn off the lights and set the alarm</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
